--- a/VerveStacks_DZA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_DZA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DZA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6362FB8-0A5D-4CE0-9E92-741F01BA14A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F290D41-AC9E-4CDD-97AE-1461A79CC516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4983,7 +4983,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9B065CF-E0A8-4C0B-8417-EA5601E31DD4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{240AD10E-9C87-4435-A5F1-235889E4399D}">
   <dimension ref="B2:AE493"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_DZA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_DZA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DZA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F290D41-AC9E-4CDD-97AE-1461A79CC516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{61C7C201-05DB-4808-9B68-1B6533221087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4983,7 +4983,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{240AD10E-9C87-4435-A5F1-235889E4399D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BFF7E5C-2E48-4BA8-ACE6-E7403007AA2A}">
   <dimension ref="B2:AE493"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_DZA_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_DZA_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DZA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C486D4F-8EFC-4C6E-94CD-309A90832424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E34351A-F102-4EEB-8E4D-F06F0043F15E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3594" uniqueCount="660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3670" uniqueCount="680">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -1137,6 +1137,45 @@
     <t>Steam Coal - ULTRASUPERCRITICAL_DZ113-400</t>
   </si>
   <si>
+    <t>Bioenergy + CCUS_w610844609-400</t>
+  </si>
+  <si>
+    <t>Bioenergy - Large scale unit_w610844609-400</t>
+  </si>
+  <si>
+    <t>CCGT_w610844609-400</t>
+  </si>
+  <si>
+    <t>CCGT + CCS_w610844609-400</t>
+  </si>
+  <si>
+    <t>Coal + CCS_w610844609-400</t>
+  </si>
+  <si>
+    <t>Gas turbine_w610844609-400</t>
+  </si>
+  <si>
+    <t>IGCC_w610844609-400</t>
+  </si>
+  <si>
+    <t>IGCC + CCS_w610844609-400</t>
+  </si>
+  <si>
+    <t>Nuclear large_w610844609-400</t>
+  </si>
+  <si>
+    <t>Oxyfuel + CCS_w610844609-400</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUBCRITICAL_w610844609-400</t>
+  </si>
+  <si>
+    <t>Steam Coal - SUPERCRITICAL_w610844609-400</t>
+  </si>
+  <si>
+    <t>Steam Coal - ULTRASUPERCRITICAL_w610844609-400</t>
+  </si>
+  <si>
     <t>Bioenergy + CCUS_w226912498-400</t>
   </si>
   <si>
@@ -1965,6 +2004,12 @@
     <t>EN_STG4hbNREL_DZ113-400</t>
   </si>
   <si>
+    <t>EN_STG8hbNREL_w610844609-400</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_w610844609-400</t>
+  </si>
+  <si>
     <t>EN_STG8hbNREL_w226912498-400</t>
   </si>
   <si>
@@ -2077,6 +2122,21 @@
   </si>
   <si>
     <t>EN_STG4hbNREL_w176932220-400</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_DZ139-400</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_DZ139-400</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_DZ135-400</t>
+  </si>
+  <si>
+    <t>e_DZ135-400</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_DZ135-400</t>
   </si>
   <si>
     <t>EN_STG8hbNREL_DZ63-400</t>
@@ -2589,8 +2649,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{594D2C14-4456-4616-A7CB-B51F9B7F6A49}">
-  <dimension ref="B2:AE383"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5831768E-0CD5-4B6B-B224-4F0E20E9936B}">
+  <dimension ref="B2:AE402"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="2" spans="2:31" x14ac:dyDescent="0.45">
@@ -2713,16 +2773,16 @@
         <v>157</v>
       </c>
       <c r="AB4" t="s">
-        <v>654</v>
+        <v>674</v>
       </c>
       <c r="AC4" t="s">
-        <v>656</v>
+        <v>676</v>
       </c>
       <c r="AD4" t="s">
-        <v>657</v>
+        <v>677</v>
       </c>
       <c r="AE4" t="s">
-        <v>658</v>
+        <v>678</v>
       </c>
     </row>
     <row r="5" spans="2:31" x14ac:dyDescent="0.45">
@@ -2775,10 +2835,10 @@
         <v>257</v>
       </c>
       <c r="AA5" t="s">
-        <v>653</v>
+        <v>673</v>
       </c>
       <c r="AB5" t="s">
-        <v>655</v>
+        <v>675</v>
       </c>
       <c r="AC5">
         <v>2</v>
@@ -2787,7 +2847,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="s">
-        <v>659</v>
+        <v>679</v>
       </c>
     </row>
     <row r="6" spans="2:31" x14ac:dyDescent="0.45">
@@ -6250,7 +6310,7 @@
         <v>337</v>
       </c>
       <c r="W82" t="s">
-        <v>338</v>
+        <v>246</v>
       </c>
       <c r="X82" t="s">
         <v>257</v>
@@ -6261,10 +6321,10 @@
         <v>91</v>
       </c>
       <c r="V83" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="W83" t="s">
-        <v>338</v>
+        <v>246</v>
       </c>
       <c r="X83" t="s">
         <v>257</v>
@@ -6275,10 +6335,10 @@
         <v>91</v>
       </c>
       <c r="V84" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="W84" t="s">
-        <v>338</v>
+        <v>246</v>
       </c>
       <c r="X84" t="s">
         <v>257</v>
@@ -6289,10 +6349,10 @@
         <v>91</v>
       </c>
       <c r="V85" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="W85" t="s">
-        <v>338</v>
+        <v>246</v>
       </c>
       <c r="X85" t="s">
         <v>257</v>
@@ -6303,10 +6363,10 @@
         <v>91</v>
       </c>
       <c r="V86" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="W86" t="s">
-        <v>338</v>
+        <v>246</v>
       </c>
       <c r="X86" t="s">
         <v>257</v>
@@ -6317,10 +6377,10 @@
         <v>91</v>
       </c>
       <c r="V87" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="W87" t="s">
-        <v>338</v>
+        <v>246</v>
       </c>
       <c r="X87" t="s">
         <v>257</v>
@@ -6331,10 +6391,10 @@
         <v>91</v>
       </c>
       <c r="V88" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="W88" t="s">
-        <v>338</v>
+        <v>246</v>
       </c>
       <c r="X88" t="s">
         <v>257</v>
@@ -6345,10 +6405,10 @@
         <v>91</v>
       </c>
       <c r="V89" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="W89" t="s">
-        <v>338</v>
+        <v>246</v>
       </c>
       <c r="X89" t="s">
         <v>257</v>
@@ -6359,10 +6419,10 @@
         <v>91</v>
       </c>
       <c r="V90" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="W90" t="s">
-        <v>338</v>
+        <v>246</v>
       </c>
       <c r="X90" t="s">
         <v>257</v>
@@ -6373,10 +6433,10 @@
         <v>91</v>
       </c>
       <c r="V91" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="W91" t="s">
-        <v>338</v>
+        <v>246</v>
       </c>
       <c r="X91" t="s">
         <v>257</v>
@@ -6387,10 +6447,10 @@
         <v>91</v>
       </c>
       <c r="V92" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="W92" t="s">
-        <v>338</v>
+        <v>246</v>
       </c>
       <c r="X92" t="s">
         <v>257</v>
@@ -6401,10 +6461,10 @@
         <v>91</v>
       </c>
       <c r="V93" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="W93" t="s">
-        <v>338</v>
+        <v>246</v>
       </c>
       <c r="X93" t="s">
         <v>257</v>
@@ -6415,10 +6475,10 @@
         <v>91</v>
       </c>
       <c r="V94" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="W94" t="s">
-        <v>338</v>
+        <v>246</v>
       </c>
       <c r="X94" t="s">
         <v>257</v>
@@ -6429,10 +6489,10 @@
         <v>91</v>
       </c>
       <c r="V95" t="s">
+        <v>350</v>
+      </c>
+      <c r="W95" t="s">
         <v>351</v>
-      </c>
-      <c r="W95" t="s">
-        <v>352</v>
       </c>
       <c r="X95" t="s">
         <v>257</v>
@@ -6443,10 +6503,10 @@
         <v>91</v>
       </c>
       <c r="V96" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="W96" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="X96" t="s">
         <v>257</v>
@@ -6457,10 +6517,10 @@
         <v>91</v>
       </c>
       <c r="V97" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="W97" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="X97" t="s">
         <v>257</v>
@@ -6471,10 +6531,10 @@
         <v>91</v>
       </c>
       <c r="V98" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="W98" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="X98" t="s">
         <v>257</v>
@@ -6485,10 +6545,10 @@
         <v>91</v>
       </c>
       <c r="V99" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="W99" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="X99" t="s">
         <v>257</v>
@@ -6499,10 +6559,10 @@
         <v>91</v>
       </c>
       <c r="V100" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="W100" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="X100" t="s">
         <v>257</v>
@@ -6513,10 +6573,10 @@
         <v>91</v>
       </c>
       <c r="V101" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="W101" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="X101" t="s">
         <v>257</v>
@@ -6527,10 +6587,10 @@
         <v>91</v>
       </c>
       <c r="V102" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="W102" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="X102" t="s">
         <v>257</v>
@@ -6541,10 +6601,10 @@
         <v>91</v>
       </c>
       <c r="V103" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="W103" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="X103" t="s">
         <v>257</v>
@@ -6555,10 +6615,10 @@
         <v>91</v>
       </c>
       <c r="V104" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="W104" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="X104" t="s">
         <v>257</v>
@@ -6569,10 +6629,10 @@
         <v>91</v>
       </c>
       <c r="V105" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="W105" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="X105" t="s">
         <v>257</v>
@@ -6583,10 +6643,10 @@
         <v>91</v>
       </c>
       <c r="V106" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="W106" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="X106" t="s">
         <v>257</v>
@@ -6597,10 +6657,10 @@
         <v>91</v>
       </c>
       <c r="V107" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="W107" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="X107" t="s">
         <v>257</v>
@@ -6611,10 +6671,10 @@
         <v>91</v>
       </c>
       <c r="V108" t="s">
+        <v>364</v>
+      </c>
+      <c r="W108" t="s">
         <v>365</v>
-      </c>
-      <c r="W108" t="s">
-        <v>251</v>
       </c>
       <c r="X108" t="s">
         <v>257</v>
@@ -6628,7 +6688,7 @@
         <v>366</v>
       </c>
       <c r="W109" t="s">
-        <v>251</v>
+        <v>365</v>
       </c>
       <c r="X109" t="s">
         <v>257</v>
@@ -6642,7 +6702,7 @@
         <v>367</v>
       </c>
       <c r="W110" t="s">
-        <v>251</v>
+        <v>365</v>
       </c>
       <c r="X110" t="s">
         <v>257</v>
@@ -6656,7 +6716,7 @@
         <v>368</v>
       </c>
       <c r="W111" t="s">
-        <v>251</v>
+        <v>365</v>
       </c>
       <c r="X111" t="s">
         <v>257</v>
@@ -6670,7 +6730,7 @@
         <v>369</v>
       </c>
       <c r="W112" t="s">
-        <v>251</v>
+        <v>365</v>
       </c>
       <c r="X112" t="s">
         <v>257</v>
@@ -6684,7 +6744,7 @@
         <v>370</v>
       </c>
       <c r="W113" t="s">
-        <v>251</v>
+        <v>365</v>
       </c>
       <c r="X113" t="s">
         <v>257</v>
@@ -6698,7 +6758,7 @@
         <v>371</v>
       </c>
       <c r="W114" t="s">
-        <v>251</v>
+        <v>365</v>
       </c>
       <c r="X114" t="s">
         <v>257</v>
@@ -6712,7 +6772,7 @@
         <v>372</v>
       </c>
       <c r="W115" t="s">
-        <v>251</v>
+        <v>365</v>
       </c>
       <c r="X115" t="s">
         <v>257</v>
@@ -6726,7 +6786,7 @@
         <v>373</v>
       </c>
       <c r="W116" t="s">
-        <v>251</v>
+        <v>365</v>
       </c>
       <c r="X116" t="s">
         <v>257</v>
@@ -6740,7 +6800,7 @@
         <v>374</v>
       </c>
       <c r="W117" t="s">
-        <v>251</v>
+        <v>365</v>
       </c>
       <c r="X117" t="s">
         <v>257</v>
@@ -6754,7 +6814,7 @@
         <v>375</v>
       </c>
       <c r="W118" t="s">
-        <v>251</v>
+        <v>365</v>
       </c>
       <c r="X118" t="s">
         <v>257</v>
@@ -6768,7 +6828,7 @@
         <v>376</v>
       </c>
       <c r="W119" t="s">
-        <v>251</v>
+        <v>365</v>
       </c>
       <c r="X119" t="s">
         <v>257</v>
@@ -6782,7 +6842,7 @@
         <v>377</v>
       </c>
       <c r="W120" t="s">
-        <v>251</v>
+        <v>365</v>
       </c>
       <c r="X120" t="s">
         <v>257</v>
@@ -6796,7 +6856,7 @@
         <v>378</v>
       </c>
       <c r="W121" t="s">
-        <v>379</v>
+        <v>251</v>
       </c>
       <c r="X121" t="s">
         <v>257</v>
@@ -6807,10 +6867,10 @@
         <v>91</v>
       </c>
       <c r="V122" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="W122" t="s">
-        <v>379</v>
+        <v>251</v>
       </c>
       <c r="X122" t="s">
         <v>257</v>
@@ -6821,10 +6881,10 @@
         <v>91</v>
       </c>
       <c r="V123" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="W123" t="s">
-        <v>379</v>
+        <v>251</v>
       </c>
       <c r="X123" t="s">
         <v>257</v>
@@ -6835,10 +6895,10 @@
         <v>91</v>
       </c>
       <c r="V124" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="W124" t="s">
-        <v>379</v>
+        <v>251</v>
       </c>
       <c r="X124" t="s">
         <v>257</v>
@@ -6849,10 +6909,10 @@
         <v>91</v>
       </c>
       <c r="V125" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="W125" t="s">
-        <v>379</v>
+        <v>251</v>
       </c>
       <c r="X125" t="s">
         <v>257</v>
@@ -6863,10 +6923,10 @@
         <v>91</v>
       </c>
       <c r="V126" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="W126" t="s">
-        <v>379</v>
+        <v>251</v>
       </c>
       <c r="X126" t="s">
         <v>257</v>
@@ -6877,10 +6937,10 @@
         <v>91</v>
       </c>
       <c r="V127" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="W127" t="s">
-        <v>379</v>
+        <v>251</v>
       </c>
       <c r="X127" t="s">
         <v>257</v>
@@ -6891,10 +6951,10 @@
         <v>91</v>
       </c>
       <c r="V128" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="W128" t="s">
-        <v>379</v>
+        <v>251</v>
       </c>
       <c r="X128" t="s">
         <v>257</v>
@@ -6905,10 +6965,10 @@
         <v>91</v>
       </c>
       <c r="V129" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="W129" t="s">
-        <v>379</v>
+        <v>251</v>
       </c>
       <c r="X129" t="s">
         <v>257</v>
@@ -6919,10 +6979,10 @@
         <v>91</v>
       </c>
       <c r="V130" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="W130" t="s">
-        <v>379</v>
+        <v>251</v>
       </c>
       <c r="X130" t="s">
         <v>257</v>
@@ -6933,10 +6993,10 @@
         <v>91</v>
       </c>
       <c r="V131" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="W131" t="s">
-        <v>379</v>
+        <v>251</v>
       </c>
       <c r="X131" t="s">
         <v>257</v>
@@ -6947,10 +7007,10 @@
         <v>91</v>
       </c>
       <c r="V132" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="W132" t="s">
-        <v>379</v>
+        <v>251</v>
       </c>
       <c r="X132" t="s">
         <v>257</v>
@@ -6961,10 +7021,10 @@
         <v>91</v>
       </c>
       <c r="V133" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="W133" t="s">
-        <v>379</v>
+        <v>251</v>
       </c>
       <c r="X133" t="s">
         <v>257</v>
@@ -6975,10 +7035,10 @@
         <v>91</v>
       </c>
       <c r="V134" t="s">
+        <v>391</v>
+      </c>
+      <c r="W134" t="s">
         <v>392</v>
-      </c>
-      <c r="W134" t="s">
-        <v>393</v>
       </c>
       <c r="X134" t="s">
         <v>257</v>
@@ -6989,10 +7049,10 @@
         <v>91</v>
       </c>
       <c r="V135" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="W135" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="X135" t="s">
         <v>257</v>
@@ -7003,10 +7063,10 @@
         <v>91</v>
       </c>
       <c r="V136" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="W136" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="X136" t="s">
         <v>257</v>
@@ -7017,10 +7077,10 @@
         <v>91</v>
       </c>
       <c r="V137" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="W137" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="X137" t="s">
         <v>257</v>
@@ -7031,10 +7091,10 @@
         <v>91</v>
       </c>
       <c r="V138" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="W138" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="X138" t="s">
         <v>257</v>
@@ -7045,10 +7105,10 @@
         <v>91</v>
       </c>
       <c r="V139" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="W139" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="X139" t="s">
         <v>257</v>
@@ -7059,10 +7119,10 @@
         <v>91</v>
       </c>
       <c r="V140" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="W140" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="X140" t="s">
         <v>257</v>
@@ -7073,10 +7133,10 @@
         <v>91</v>
       </c>
       <c r="V141" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="W141" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="X141" t="s">
         <v>257</v>
@@ -7087,10 +7147,10 @@
         <v>91</v>
       </c>
       <c r="V142" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="W142" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="X142" t="s">
         <v>257</v>
@@ -7101,10 +7161,10 @@
         <v>91</v>
       </c>
       <c r="V143" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="W143" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="X143" t="s">
         <v>257</v>
@@ -7115,10 +7175,10 @@
         <v>91</v>
       </c>
       <c r="V144" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="W144" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="X144" t="s">
         <v>257</v>
@@ -7129,10 +7189,10 @@
         <v>91</v>
       </c>
       <c r="V145" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="W145" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="X145" t="s">
         <v>257</v>
@@ -7143,10 +7203,10 @@
         <v>91</v>
       </c>
       <c r="V146" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="W146" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="X146" t="s">
         <v>257</v>
@@ -7157,10 +7217,10 @@
         <v>91</v>
       </c>
       <c r="V147" t="s">
+        <v>405</v>
+      </c>
+      <c r="W147" t="s">
         <v>406</v>
-      </c>
-      <c r="W147" t="s">
-        <v>244</v>
       </c>
       <c r="X147" t="s">
         <v>257</v>
@@ -7174,7 +7234,7 @@
         <v>407</v>
       </c>
       <c r="W148" t="s">
-        <v>244</v>
+        <v>406</v>
       </c>
       <c r="X148" t="s">
         <v>257</v>
@@ -7188,7 +7248,7 @@
         <v>408</v>
       </c>
       <c r="W149" t="s">
-        <v>244</v>
+        <v>406</v>
       </c>
       <c r="X149" t="s">
         <v>257</v>
@@ -7202,7 +7262,7 @@
         <v>409</v>
       </c>
       <c r="W150" t="s">
-        <v>244</v>
+        <v>406</v>
       </c>
       <c r="X150" t="s">
         <v>257</v>
@@ -7216,7 +7276,7 @@
         <v>410</v>
       </c>
       <c r="W151" t="s">
-        <v>244</v>
+        <v>406</v>
       </c>
       <c r="X151" t="s">
         <v>257</v>
@@ -7230,7 +7290,7 @@
         <v>411</v>
       </c>
       <c r="W152" t="s">
-        <v>244</v>
+        <v>406</v>
       </c>
       <c r="X152" t="s">
         <v>257</v>
@@ -7244,7 +7304,7 @@
         <v>412</v>
       </c>
       <c r="W153" t="s">
-        <v>244</v>
+        <v>406</v>
       </c>
       <c r="X153" t="s">
         <v>257</v>
@@ -7258,7 +7318,7 @@
         <v>413</v>
       </c>
       <c r="W154" t="s">
-        <v>244</v>
+        <v>406</v>
       </c>
       <c r="X154" t="s">
         <v>257</v>
@@ -7272,7 +7332,7 @@
         <v>414</v>
       </c>
       <c r="W155" t="s">
-        <v>244</v>
+        <v>406</v>
       </c>
       <c r="X155" t="s">
         <v>257</v>
@@ -7286,7 +7346,7 @@
         <v>415</v>
       </c>
       <c r="W156" t="s">
-        <v>244</v>
+        <v>406</v>
       </c>
       <c r="X156" t="s">
         <v>257</v>
@@ -7300,7 +7360,7 @@
         <v>416</v>
       </c>
       <c r="W157" t="s">
-        <v>244</v>
+        <v>406</v>
       </c>
       <c r="X157" t="s">
         <v>257</v>
@@ -7314,7 +7374,7 @@
         <v>417</v>
       </c>
       <c r="W158" t="s">
-        <v>244</v>
+        <v>406</v>
       </c>
       <c r="X158" t="s">
         <v>257</v>
@@ -7328,7 +7388,7 @@
         <v>418</v>
       </c>
       <c r="W159" t="s">
-        <v>244</v>
+        <v>406</v>
       </c>
       <c r="X159" t="s">
         <v>257</v>
@@ -7342,7 +7402,7 @@
         <v>419</v>
       </c>
       <c r="W160" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="X160" t="s">
         <v>257</v>
@@ -7356,7 +7416,7 @@
         <v>420</v>
       </c>
       <c r="W161" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="X161" t="s">
         <v>257</v>
@@ -7370,7 +7430,7 @@
         <v>421</v>
       </c>
       <c r="W162" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="X162" t="s">
         <v>257</v>
@@ -7384,7 +7444,7 @@
         <v>422</v>
       </c>
       <c r="W163" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="X163" t="s">
         <v>257</v>
@@ -7398,7 +7458,7 @@
         <v>423</v>
       </c>
       <c r="W164" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="X164" t="s">
         <v>257</v>
@@ -7412,7 +7472,7 @@
         <v>424</v>
       </c>
       <c r="W165" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="X165" t="s">
         <v>257</v>
@@ -7426,7 +7486,7 @@
         <v>425</v>
       </c>
       <c r="W166" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="X166" t="s">
         <v>257</v>
@@ -7440,7 +7500,7 @@
         <v>426</v>
       </c>
       <c r="W167" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="X167" t="s">
         <v>257</v>
@@ -7454,7 +7514,7 @@
         <v>427</v>
       </c>
       <c r="W168" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="X168" t="s">
         <v>257</v>
@@ -7468,7 +7528,7 @@
         <v>428</v>
       </c>
       <c r="W169" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="X169" t="s">
         <v>257</v>
@@ -7482,7 +7542,7 @@
         <v>429</v>
       </c>
       <c r="W170" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="X170" t="s">
         <v>257</v>
@@ -7496,7 +7556,7 @@
         <v>430</v>
       </c>
       <c r="W171" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="X171" t="s">
         <v>257</v>
@@ -7510,7 +7570,7 @@
         <v>431</v>
       </c>
       <c r="W172" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="X172" t="s">
         <v>257</v>
@@ -7524,7 +7584,7 @@
         <v>432</v>
       </c>
       <c r="W173" t="s">
-        <v>433</v>
+        <v>248</v>
       </c>
       <c r="X173" t="s">
         <v>257</v>
@@ -7535,10 +7595,10 @@
         <v>91</v>
       </c>
       <c r="V174" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="W174" t="s">
-        <v>433</v>
+        <v>248</v>
       </c>
       <c r="X174" t="s">
         <v>257</v>
@@ -7549,10 +7609,10 @@
         <v>91</v>
       </c>
       <c r="V175" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="W175" t="s">
-        <v>433</v>
+        <v>248</v>
       </c>
       <c r="X175" t="s">
         <v>257</v>
@@ -7563,10 +7623,10 @@
         <v>91</v>
       </c>
       <c r="V176" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="W176" t="s">
-        <v>433</v>
+        <v>248</v>
       </c>
       <c r="X176" t="s">
         <v>257</v>
@@ -7577,10 +7637,10 @@
         <v>91</v>
       </c>
       <c r="V177" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="W177" t="s">
-        <v>433</v>
+        <v>248</v>
       </c>
       <c r="X177" t="s">
         <v>257</v>
@@ -7591,10 +7651,10 @@
         <v>91</v>
       </c>
       <c r="V178" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="W178" t="s">
-        <v>433</v>
+        <v>248</v>
       </c>
       <c r="X178" t="s">
         <v>257</v>
@@ -7605,10 +7665,10 @@
         <v>91</v>
       </c>
       <c r="V179" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="W179" t="s">
-        <v>433</v>
+        <v>248</v>
       </c>
       <c r="X179" t="s">
         <v>257</v>
@@ -7619,10 +7679,10 @@
         <v>91</v>
       </c>
       <c r="V180" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="W180" t="s">
-        <v>433</v>
+        <v>248</v>
       </c>
       <c r="X180" t="s">
         <v>257</v>
@@ -7633,10 +7693,10 @@
         <v>91</v>
       </c>
       <c r="V181" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="W181" t="s">
-        <v>433</v>
+        <v>248</v>
       </c>
       <c r="X181" t="s">
         <v>257</v>
@@ -7647,10 +7707,10 @@
         <v>91</v>
       </c>
       <c r="V182" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="W182" t="s">
-        <v>433</v>
+        <v>248</v>
       </c>
       <c r="X182" t="s">
         <v>257</v>
@@ -7661,10 +7721,10 @@
         <v>91</v>
       </c>
       <c r="V183" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="W183" t="s">
-        <v>433</v>
+        <v>248</v>
       </c>
       <c r="X183" t="s">
         <v>257</v>
@@ -7675,10 +7735,10 @@
         <v>91</v>
       </c>
       <c r="V184" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="W184" t="s">
-        <v>433</v>
+        <v>248</v>
       </c>
       <c r="X184" t="s">
         <v>257</v>
@@ -7689,10 +7749,10 @@
         <v>91</v>
       </c>
       <c r="V185" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="W185" t="s">
-        <v>433</v>
+        <v>248</v>
       </c>
       <c r="X185" t="s">
         <v>257</v>
@@ -7703,10 +7763,10 @@
         <v>91</v>
       </c>
       <c r="V186" t="s">
+        <v>445</v>
+      </c>
+      <c r="W186" t="s">
         <v>446</v>
-      </c>
-      <c r="W186" t="s">
-        <v>447</v>
       </c>
       <c r="X186" t="s">
         <v>257</v>
@@ -7717,10 +7777,10 @@
         <v>91</v>
       </c>
       <c r="V187" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="W187" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="X187" t="s">
         <v>257</v>
@@ -7731,10 +7791,10 @@
         <v>91</v>
       </c>
       <c r="V188" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="W188" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="X188" t="s">
         <v>257</v>
@@ -7745,10 +7805,10 @@
         <v>91</v>
       </c>
       <c r="V189" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="W189" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="X189" t="s">
         <v>257</v>
@@ -7759,10 +7819,10 @@
         <v>91</v>
       </c>
       <c r="V190" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="W190" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="X190" t="s">
         <v>257</v>
@@ -7773,10 +7833,10 @@
         <v>91</v>
       </c>
       <c r="V191" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="W191" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="X191" t="s">
         <v>257</v>
@@ -7787,10 +7847,10 @@
         <v>91</v>
       </c>
       <c r="V192" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="W192" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="X192" t="s">
         <v>257</v>
@@ -7801,10 +7861,10 @@
         <v>91</v>
       </c>
       <c r="V193" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="W193" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="X193" t="s">
         <v>257</v>
@@ -7815,10 +7875,10 @@
         <v>91</v>
       </c>
       <c r="V194" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="W194" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="X194" t="s">
         <v>257</v>
@@ -7829,10 +7889,10 @@
         <v>91</v>
       </c>
       <c r="V195" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="W195" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="X195" t="s">
         <v>257</v>
@@ -7843,10 +7903,10 @@
         <v>91</v>
       </c>
       <c r="V196" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="W196" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="X196" t="s">
         <v>257</v>
@@ -7857,10 +7917,10 @@
         <v>91</v>
       </c>
       <c r="V197" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="W197" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="X197" t="s">
         <v>257</v>
@@ -7871,10 +7931,10 @@
         <v>91</v>
       </c>
       <c r="V198" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="W198" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="X198" t="s">
         <v>257</v>
@@ -7885,10 +7945,10 @@
         <v>91</v>
       </c>
       <c r="V199" t="s">
+        <v>459</v>
+      </c>
+      <c r="W199" t="s">
         <v>460</v>
-      </c>
-      <c r="W199" t="s">
-        <v>461</v>
       </c>
       <c r="X199" t="s">
         <v>257</v>
@@ -7899,10 +7959,10 @@
         <v>91</v>
       </c>
       <c r="V200" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="W200" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="X200" t="s">
         <v>257</v>
@@ -7913,10 +7973,10 @@
         <v>91</v>
       </c>
       <c r="V201" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="W201" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="X201" t="s">
         <v>257</v>
@@ -7927,10 +7987,10 @@
         <v>91</v>
       </c>
       <c r="V202" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="W202" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="X202" t="s">
         <v>257</v>
@@ -7941,10 +8001,10 @@
         <v>91</v>
       </c>
       <c r="V203" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="W203" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="X203" t="s">
         <v>257</v>
@@ -7955,10 +8015,10 @@
         <v>91</v>
       </c>
       <c r="V204" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="W204" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="X204" t="s">
         <v>257</v>
@@ -7969,10 +8029,10 @@
         <v>91</v>
       </c>
       <c r="V205" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="W205" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="X205" t="s">
         <v>257</v>
@@ -7983,10 +8043,10 @@
         <v>91</v>
       </c>
       <c r="V206" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="W206" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="X206" t="s">
         <v>257</v>
@@ -7997,10 +8057,10 @@
         <v>91</v>
       </c>
       <c r="V207" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="W207" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="X207" t="s">
         <v>257</v>
@@ -8011,10 +8071,10 @@
         <v>91</v>
       </c>
       <c r="V208" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="W208" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="X208" t="s">
         <v>257</v>
@@ -8025,10 +8085,10 @@
         <v>91</v>
       </c>
       <c r="V209" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="W209" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="X209" t="s">
         <v>257</v>
@@ -8039,10 +8099,10 @@
         <v>91</v>
       </c>
       <c r="V210" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="W210" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="X210" t="s">
         <v>257</v>
@@ -8053,10 +8113,10 @@
         <v>91</v>
       </c>
       <c r="V211" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="W211" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="X211" t="s">
         <v>257</v>
@@ -8067,10 +8127,10 @@
         <v>91</v>
       </c>
       <c r="V212" t="s">
+        <v>473</v>
+      </c>
+      <c r="W212" t="s">
         <v>474</v>
-      </c>
-      <c r="W212" t="s">
-        <v>475</v>
       </c>
       <c r="X212" t="s">
         <v>257</v>
@@ -8081,10 +8141,10 @@
         <v>91</v>
       </c>
       <c r="V213" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="W213" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="X213" t="s">
         <v>257</v>
@@ -8095,10 +8155,10 @@
         <v>91</v>
       </c>
       <c r="V214" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="W214" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="X214" t="s">
         <v>257</v>
@@ -8109,10 +8169,10 @@
         <v>91</v>
       </c>
       <c r="V215" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="W215" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="X215" t="s">
         <v>257</v>
@@ -8123,10 +8183,10 @@
         <v>91</v>
       </c>
       <c r="V216" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="W216" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="X216" t="s">
         <v>257</v>
@@ -8137,10 +8197,10 @@
         <v>91</v>
       </c>
       <c r="V217" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="W217" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="X217" t="s">
         <v>257</v>
@@ -8151,10 +8211,10 @@
         <v>91</v>
       </c>
       <c r="V218" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="W218" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="X218" t="s">
         <v>257</v>
@@ -8165,10 +8225,10 @@
         <v>91</v>
       </c>
       <c r="V219" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="W219" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="X219" t="s">
         <v>257</v>
@@ -8179,10 +8239,10 @@
         <v>91</v>
       </c>
       <c r="V220" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="W220" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="X220" t="s">
         <v>257</v>
@@ -8193,10 +8253,10 @@
         <v>91</v>
       </c>
       <c r="V221" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="W221" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="X221" t="s">
         <v>257</v>
@@ -8207,10 +8267,10 @@
         <v>91</v>
       </c>
       <c r="V222" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="W222" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="X222" t="s">
         <v>257</v>
@@ -8221,10 +8281,10 @@
         <v>91</v>
       </c>
       <c r="V223" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="W223" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="X223" t="s">
         <v>257</v>
@@ -8235,10 +8295,10 @@
         <v>91</v>
       </c>
       <c r="V224" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="W224" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="X224" t="s">
         <v>257</v>
@@ -8249,10 +8309,10 @@
         <v>91</v>
       </c>
       <c r="V225" t="s">
+        <v>487</v>
+      </c>
+      <c r="W225" t="s">
         <v>488</v>
-      </c>
-      <c r="W225" t="s">
-        <v>489</v>
       </c>
       <c r="X225" t="s">
         <v>257</v>
@@ -8263,10 +8323,10 @@
         <v>91</v>
       </c>
       <c r="V226" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="W226" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="X226" t="s">
         <v>257</v>
@@ -8277,10 +8337,10 @@
         <v>91</v>
       </c>
       <c r="V227" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="W227" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="X227" t="s">
         <v>257</v>
@@ -8291,10 +8351,10 @@
         <v>91</v>
       </c>
       <c r="V228" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="W228" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="X228" t="s">
         <v>257</v>
@@ -8305,10 +8365,10 @@
         <v>91</v>
       </c>
       <c r="V229" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="W229" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="X229" t="s">
         <v>257</v>
@@ -8319,10 +8379,10 @@
         <v>91</v>
       </c>
       <c r="V230" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="W230" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="X230" t="s">
         <v>257</v>
@@ -8333,10 +8393,10 @@
         <v>91</v>
       </c>
       <c r="V231" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="W231" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="X231" t="s">
         <v>257</v>
@@ -8347,10 +8407,10 @@
         <v>91</v>
       </c>
       <c r="V232" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="W232" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="X232" t="s">
         <v>257</v>
@@ -8361,10 +8421,10 @@
         <v>91</v>
       </c>
       <c r="V233" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="W233" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="X233" t="s">
         <v>257</v>
@@ -8375,10 +8435,10 @@
         <v>91</v>
       </c>
       <c r="V234" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="W234" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="X234" t="s">
         <v>257</v>
@@ -8389,10 +8449,10 @@
         <v>91</v>
       </c>
       <c r="V235" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="W235" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="X235" t="s">
         <v>257</v>
@@ -8403,10 +8463,10 @@
         <v>91</v>
       </c>
       <c r="V236" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="W236" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="X236" t="s">
         <v>257</v>
@@ -8417,10 +8477,10 @@
         <v>91</v>
       </c>
       <c r="V237" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="W237" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="X237" t="s">
         <v>257</v>
@@ -8431,10 +8491,10 @@
         <v>91</v>
       </c>
       <c r="V238" t="s">
+        <v>501</v>
+      </c>
+      <c r="W238" t="s">
         <v>502</v>
-      </c>
-      <c r="W238" t="s">
-        <v>242</v>
       </c>
       <c r="X238" t="s">
         <v>257</v>
@@ -8448,7 +8508,7 @@
         <v>503</v>
       </c>
       <c r="W239" t="s">
-        <v>242</v>
+        <v>502</v>
       </c>
       <c r="X239" t="s">
         <v>257</v>
@@ -8462,7 +8522,7 @@
         <v>504</v>
       </c>
       <c r="W240" t="s">
-        <v>242</v>
+        <v>502</v>
       </c>
       <c r="X240" t="s">
         <v>257</v>
@@ -8476,7 +8536,7 @@
         <v>505</v>
       </c>
       <c r="W241" t="s">
-        <v>242</v>
+        <v>502</v>
       </c>
       <c r="X241" t="s">
         <v>257</v>
@@ -8490,7 +8550,7 @@
         <v>506</v>
       </c>
       <c r="W242" t="s">
-        <v>242</v>
+        <v>502</v>
       </c>
       <c r="X242" t="s">
         <v>257</v>
@@ -8504,7 +8564,7 @@
         <v>507</v>
       </c>
       <c r="W243" t="s">
-        <v>242</v>
+        <v>502</v>
       </c>
       <c r="X243" t="s">
         <v>257</v>
@@ -8518,7 +8578,7 @@
         <v>508</v>
       </c>
       <c r="W244" t="s">
-        <v>242</v>
+        <v>502</v>
       </c>
       <c r="X244" t="s">
         <v>257</v>
@@ -8532,7 +8592,7 @@
         <v>509</v>
       </c>
       <c r="W245" t="s">
-        <v>242</v>
+        <v>502</v>
       </c>
       <c r="X245" t="s">
         <v>257</v>
@@ -8546,7 +8606,7 @@
         <v>510</v>
       </c>
       <c r="W246" t="s">
-        <v>242</v>
+        <v>502</v>
       </c>
       <c r="X246" t="s">
         <v>257</v>
@@ -8560,7 +8620,7 @@
         <v>511</v>
       </c>
       <c r="W247" t="s">
-        <v>242</v>
+        <v>502</v>
       </c>
       <c r="X247" t="s">
         <v>257</v>
@@ -8574,7 +8634,7 @@
         <v>512</v>
       </c>
       <c r="W248" t="s">
-        <v>242</v>
+        <v>502</v>
       </c>
       <c r="X248" t="s">
         <v>257</v>
@@ -8588,7 +8648,7 @@
         <v>513</v>
       </c>
       <c r="W249" t="s">
-        <v>242</v>
+        <v>502</v>
       </c>
       <c r="X249" t="s">
         <v>257</v>
@@ -8602,7 +8662,7 @@
         <v>514</v>
       </c>
       <c r="W250" t="s">
-        <v>242</v>
+        <v>502</v>
       </c>
       <c r="X250" t="s">
         <v>257</v>
@@ -8616,7 +8676,7 @@
         <v>515</v>
       </c>
       <c r="W251" t="s">
-        <v>516</v>
+        <v>242</v>
       </c>
       <c r="X251" t="s">
         <v>257</v>
@@ -8627,10 +8687,10 @@
         <v>91</v>
       </c>
       <c r="V252" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="W252" t="s">
-        <v>516</v>
+        <v>242</v>
       </c>
       <c r="X252" t="s">
         <v>257</v>
@@ -8641,10 +8701,10 @@
         <v>91</v>
       </c>
       <c r="V253" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="W253" t="s">
-        <v>516</v>
+        <v>242</v>
       </c>
       <c r="X253" t="s">
         <v>257</v>
@@ -8655,10 +8715,10 @@
         <v>91</v>
       </c>
       <c r="V254" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="W254" t="s">
-        <v>516</v>
+        <v>242</v>
       </c>
       <c r="X254" t="s">
         <v>257</v>
@@ -8669,10 +8729,10 @@
         <v>91</v>
       </c>
       <c r="V255" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="W255" t="s">
-        <v>516</v>
+        <v>242</v>
       </c>
       <c r="X255" t="s">
         <v>257</v>
@@ -8683,10 +8743,10 @@
         <v>91</v>
       </c>
       <c r="V256" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="W256" t="s">
-        <v>516</v>
+        <v>242</v>
       </c>
       <c r="X256" t="s">
         <v>257</v>
@@ -8697,10 +8757,10 @@
         <v>91</v>
       </c>
       <c r="V257" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="W257" t="s">
-        <v>516</v>
+        <v>242</v>
       </c>
       <c r="X257" t="s">
         <v>257</v>
@@ -8711,10 +8771,10 @@
         <v>91</v>
       </c>
       <c r="V258" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="W258" t="s">
-        <v>516</v>
+        <v>242</v>
       </c>
       <c r="X258" t="s">
         <v>257</v>
@@ -8725,10 +8785,10 @@
         <v>91</v>
       </c>
       <c r="V259" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="W259" t="s">
-        <v>516</v>
+        <v>242</v>
       </c>
       <c r="X259" t="s">
         <v>257</v>
@@ -8739,10 +8799,10 @@
         <v>91</v>
       </c>
       <c r="V260" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="W260" t="s">
-        <v>516</v>
+        <v>242</v>
       </c>
       <c r="X260" t="s">
         <v>257</v>
@@ -8753,10 +8813,10 @@
         <v>91</v>
       </c>
       <c r="V261" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="W261" t="s">
-        <v>516</v>
+        <v>242</v>
       </c>
       <c r="X261" t="s">
         <v>257</v>
@@ -8767,10 +8827,10 @@
         <v>91</v>
       </c>
       <c r="V262" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="W262" t="s">
-        <v>516</v>
+        <v>242</v>
       </c>
       <c r="X262" t="s">
         <v>257</v>
@@ -8781,10 +8841,10 @@
         <v>91</v>
       </c>
       <c r="V263" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="W263" t="s">
-        <v>516</v>
+        <v>242</v>
       </c>
       <c r="X263" t="s">
         <v>257</v>
@@ -8795,10 +8855,10 @@
         <v>91</v>
       </c>
       <c r="V264" t="s">
+        <v>528</v>
+      </c>
+      <c r="W264" t="s">
         <v>529</v>
-      </c>
-      <c r="W264" t="s">
-        <v>254</v>
       </c>
       <c r="X264" t="s">
         <v>257</v>
@@ -8812,7 +8872,7 @@
         <v>530</v>
       </c>
       <c r="W265" t="s">
-        <v>254</v>
+        <v>529</v>
       </c>
       <c r="X265" t="s">
         <v>257</v>
@@ -8826,7 +8886,7 @@
         <v>531</v>
       </c>
       <c r="W266" t="s">
-        <v>254</v>
+        <v>529</v>
       </c>
       <c r="X266" t="s">
         <v>257</v>
@@ -8840,7 +8900,7 @@
         <v>532</v>
       </c>
       <c r="W267" t="s">
-        <v>254</v>
+        <v>529</v>
       </c>
       <c r="X267" t="s">
         <v>257</v>
@@ -8854,7 +8914,7 @@
         <v>533</v>
       </c>
       <c r="W268" t="s">
-        <v>254</v>
+        <v>529</v>
       </c>
       <c r="X268" t="s">
         <v>257</v>
@@ -8868,7 +8928,7 @@
         <v>534</v>
       </c>
       <c r="W269" t="s">
-        <v>254</v>
+        <v>529</v>
       </c>
       <c r="X269" t="s">
         <v>257</v>
@@ -8882,7 +8942,7 @@
         <v>535</v>
       </c>
       <c r="W270" t="s">
-        <v>254</v>
+        <v>529</v>
       </c>
       <c r="X270" t="s">
         <v>257</v>
@@ -8896,7 +8956,7 @@
         <v>536</v>
       </c>
       <c r="W271" t="s">
-        <v>254</v>
+        <v>529</v>
       </c>
       <c r="X271" t="s">
         <v>257</v>
@@ -8910,7 +8970,7 @@
         <v>537</v>
       </c>
       <c r="W272" t="s">
-        <v>254</v>
+        <v>529</v>
       </c>
       <c r="X272" t="s">
         <v>257</v>
@@ -8924,7 +8984,7 @@
         <v>538</v>
       </c>
       <c r="W273" t="s">
-        <v>254</v>
+        <v>529</v>
       </c>
       <c r="X273" t="s">
         <v>257</v>
@@ -8938,7 +8998,7 @@
         <v>539</v>
       </c>
       <c r="W274" t="s">
-        <v>254</v>
+        <v>529</v>
       </c>
       <c r="X274" t="s">
         <v>257</v>
@@ -8952,7 +9012,7 @@
         <v>540</v>
       </c>
       <c r="W275" t="s">
-        <v>254</v>
+        <v>529</v>
       </c>
       <c r="X275" t="s">
         <v>257</v>
@@ -8966,7 +9026,7 @@
         <v>541</v>
       </c>
       <c r="W276" t="s">
-        <v>254</v>
+        <v>529</v>
       </c>
       <c r="X276" t="s">
         <v>257</v>
@@ -8980,7 +9040,7 @@
         <v>542</v>
       </c>
       <c r="W277" t="s">
-        <v>543</v>
+        <v>254</v>
       </c>
       <c r="X277" t="s">
         <v>257</v>
@@ -8991,10 +9051,10 @@
         <v>91</v>
       </c>
       <c r="V278" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="W278" t="s">
-        <v>543</v>
+        <v>254</v>
       </c>
       <c r="X278" t="s">
         <v>257</v>
@@ -9005,10 +9065,10 @@
         <v>91</v>
       </c>
       <c r="V279" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="W279" t="s">
-        <v>543</v>
+        <v>254</v>
       </c>
       <c r="X279" t="s">
         <v>257</v>
@@ -9019,10 +9079,10 @@
         <v>91</v>
       </c>
       <c r="V280" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="W280" t="s">
-        <v>543</v>
+        <v>254</v>
       </c>
       <c r="X280" t="s">
         <v>257</v>
@@ -9033,10 +9093,10 @@
         <v>91</v>
       </c>
       <c r="V281" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="W281" t="s">
-        <v>543</v>
+        <v>254</v>
       </c>
       <c r="X281" t="s">
         <v>257</v>
@@ -9047,10 +9107,10 @@
         <v>91</v>
       </c>
       <c r="V282" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="W282" t="s">
-        <v>543</v>
+        <v>254</v>
       </c>
       <c r="X282" t="s">
         <v>257</v>
@@ -9061,10 +9121,10 @@
         <v>91</v>
       </c>
       <c r="V283" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="W283" t="s">
-        <v>543</v>
+        <v>254</v>
       </c>
       <c r="X283" t="s">
         <v>257</v>
@@ -9075,10 +9135,10 @@
         <v>91</v>
       </c>
       <c r="V284" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="W284" t="s">
-        <v>543</v>
+        <v>254</v>
       </c>
       <c r="X284" t="s">
         <v>257</v>
@@ -9089,10 +9149,10 @@
         <v>91</v>
       </c>
       <c r="V285" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="W285" t="s">
-        <v>543</v>
+        <v>254</v>
       </c>
       <c r="X285" t="s">
         <v>257</v>
@@ -9103,10 +9163,10 @@
         <v>91</v>
       </c>
       <c r="V286" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="W286" t="s">
-        <v>543</v>
+        <v>254</v>
       </c>
       <c r="X286" t="s">
         <v>257</v>
@@ -9117,10 +9177,10 @@
         <v>91</v>
       </c>
       <c r="V287" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="W287" t="s">
-        <v>543</v>
+        <v>254</v>
       </c>
       <c r="X287" t="s">
         <v>257</v>
@@ -9131,10 +9191,10 @@
         <v>91</v>
       </c>
       <c r="V288" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="W288" t="s">
-        <v>543</v>
+        <v>254</v>
       </c>
       <c r="X288" t="s">
         <v>257</v>
@@ -9145,10 +9205,10 @@
         <v>91</v>
       </c>
       <c r="V289" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="W289" t="s">
-        <v>543</v>
+        <v>254</v>
       </c>
       <c r="X289" t="s">
         <v>257</v>
@@ -9159,10 +9219,10 @@
         <v>91</v>
       </c>
       <c r="V290" t="s">
+        <v>555</v>
+      </c>
+      <c r="W290" t="s">
         <v>556</v>
-      </c>
-      <c r="W290" t="s">
-        <v>557</v>
       </c>
       <c r="X290" t="s">
         <v>257</v>
@@ -9173,10 +9233,10 @@
         <v>91</v>
       </c>
       <c r="V291" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="W291" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="X291" t="s">
         <v>257</v>
@@ -9187,10 +9247,10 @@
         <v>91</v>
       </c>
       <c r="V292" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="W292" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="X292" t="s">
         <v>257</v>
@@ -9201,10 +9261,10 @@
         <v>91</v>
       </c>
       <c r="V293" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="W293" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="X293" t="s">
         <v>257</v>
@@ -9215,10 +9275,10 @@
         <v>91</v>
       </c>
       <c r="V294" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="W294" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="X294" t="s">
         <v>257</v>
@@ -9229,10 +9289,10 @@
         <v>91</v>
       </c>
       <c r="V295" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="W295" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="X295" t="s">
         <v>257</v>
@@ -9243,10 +9303,10 @@
         <v>91</v>
       </c>
       <c r="V296" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="W296" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="X296" t="s">
         <v>257</v>
@@ -9257,10 +9317,10 @@
         <v>91</v>
       </c>
       <c r="V297" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="W297" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="X297" t="s">
         <v>257</v>
@@ -9271,10 +9331,10 @@
         <v>91</v>
       </c>
       <c r="V298" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="W298" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="X298" t="s">
         <v>257</v>
@@ -9285,10 +9345,10 @@
         <v>91</v>
       </c>
       <c r="V299" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="W299" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="X299" t="s">
         <v>257</v>
@@ -9299,10 +9359,10 @@
         <v>91</v>
       </c>
       <c r="V300" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="W300" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="X300" t="s">
         <v>257</v>
@@ -9313,10 +9373,10 @@
         <v>91</v>
       </c>
       <c r="V301" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="W301" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="X301" t="s">
         <v>257</v>
@@ -9327,10 +9387,10 @@
         <v>91</v>
       </c>
       <c r="V302" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="W302" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="X302" t="s">
         <v>257</v>
@@ -9341,10 +9401,10 @@
         <v>91</v>
       </c>
       <c r="V303" t="s">
+        <v>569</v>
+      </c>
+      <c r="W303" t="s">
         <v>570</v>
-      </c>
-      <c r="W303" t="s">
-        <v>571</v>
       </c>
       <c r="X303" t="s">
         <v>257</v>
@@ -9355,10 +9415,10 @@
         <v>91</v>
       </c>
       <c r="V304" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="W304" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="X304" t="s">
         <v>257</v>
@@ -9369,10 +9429,10 @@
         <v>91</v>
       </c>
       <c r="V305" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="W305" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="X305" t="s">
         <v>257</v>
@@ -9383,10 +9443,10 @@
         <v>91</v>
       </c>
       <c r="V306" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="W306" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="X306" t="s">
         <v>257</v>
@@ -9397,10 +9457,10 @@
         <v>91</v>
       </c>
       <c r="V307" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="W307" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="X307" t="s">
         <v>257</v>
@@ -9411,10 +9471,10 @@
         <v>91</v>
       </c>
       <c r="V308" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="W308" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="X308" t="s">
         <v>257</v>
@@ -9425,10 +9485,10 @@
         <v>91</v>
       </c>
       <c r="V309" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="W309" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="X309" t="s">
         <v>257</v>
@@ -9439,10 +9499,10 @@
         <v>91</v>
       </c>
       <c r="V310" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="W310" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="X310" t="s">
         <v>257</v>
@@ -9453,10 +9513,10 @@
         <v>91</v>
       </c>
       <c r="V311" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="W311" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="X311" t="s">
         <v>257</v>
@@ -9467,10 +9527,10 @@
         <v>91</v>
       </c>
       <c r="V312" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="W312" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="X312" t="s">
         <v>257</v>
@@ -9481,10 +9541,10 @@
         <v>91</v>
       </c>
       <c r="V313" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="W313" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="X313" t="s">
         <v>257</v>
@@ -9495,10 +9555,10 @@
         <v>91</v>
       </c>
       <c r="V314" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="W314" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="X314" t="s">
         <v>257</v>
@@ -9509,10 +9569,10 @@
         <v>91</v>
       </c>
       <c r="V315" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="W315" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="X315" t="s">
         <v>257</v>
@@ -9523,10 +9583,10 @@
         <v>91</v>
       </c>
       <c r="V316" t="s">
+        <v>583</v>
+      </c>
+      <c r="W316" t="s">
         <v>584</v>
-      </c>
-      <c r="W316" t="s">
-        <v>585</v>
       </c>
       <c r="X316" t="s">
         <v>257</v>
@@ -9537,10 +9597,10 @@
         <v>91</v>
       </c>
       <c r="V317" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="W317" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="X317" t="s">
         <v>257</v>
@@ -9551,10 +9611,10 @@
         <v>91</v>
       </c>
       <c r="V318" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="W318" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="X318" t="s">
         <v>257</v>
@@ -9565,10 +9625,10 @@
         <v>91</v>
       </c>
       <c r="V319" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="W319" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="X319" t="s">
         <v>257</v>
@@ -9579,10 +9639,10 @@
         <v>91</v>
       </c>
       <c r="V320" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="W320" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="X320" t="s">
         <v>257</v>
@@ -9593,10 +9653,10 @@
         <v>91</v>
       </c>
       <c r="V321" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="W321" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="X321" t="s">
         <v>257</v>
@@ -9607,10 +9667,10 @@
         <v>91</v>
       </c>
       <c r="V322" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="W322" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="X322" t="s">
         <v>257</v>
@@ -9621,10 +9681,10 @@
         <v>91</v>
       </c>
       <c r="V323" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="W323" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="X323" t="s">
         <v>257</v>
@@ -9635,10 +9695,10 @@
         <v>91</v>
       </c>
       <c r="V324" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="W324" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="X324" t="s">
         <v>257</v>
@@ -9649,10 +9709,10 @@
         <v>91</v>
       </c>
       <c r="V325" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="W325" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="X325" t="s">
         <v>257</v>
@@ -9663,10 +9723,10 @@
         <v>91</v>
       </c>
       <c r="V326" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="W326" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="X326" t="s">
         <v>257</v>
@@ -9677,10 +9737,10 @@
         <v>91</v>
       </c>
       <c r="V327" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="W327" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="X327" t="s">
         <v>257</v>
@@ -9691,10 +9751,10 @@
         <v>91</v>
       </c>
       <c r="V328" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="W328" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="X328" t="s">
         <v>257</v>
@@ -9705,10 +9765,10 @@
         <v>91</v>
       </c>
       <c r="V329" t="s">
+        <v>597</v>
+      </c>
+      <c r="W329" t="s">
         <v>598</v>
-      </c>
-      <c r="W329" t="s">
-        <v>253</v>
       </c>
       <c r="X329" t="s">
         <v>257</v>
@@ -9722,7 +9782,7 @@
         <v>599</v>
       </c>
       <c r="W330" t="s">
-        <v>253</v>
+        <v>598</v>
       </c>
       <c r="X330" t="s">
         <v>257</v>
@@ -9736,7 +9796,7 @@
         <v>600</v>
       </c>
       <c r="W331" t="s">
-        <v>253</v>
+        <v>598</v>
       </c>
       <c r="X331" t="s">
         <v>257</v>
@@ -9750,7 +9810,7 @@
         <v>601</v>
       </c>
       <c r="W332" t="s">
-        <v>250</v>
+        <v>598</v>
       </c>
       <c r="X332" t="s">
         <v>257</v>
@@ -9764,7 +9824,7 @@
         <v>602</v>
       </c>
       <c r="W333" t="s">
-        <v>250</v>
+        <v>598</v>
       </c>
       <c r="X333" t="s">
         <v>257</v>
@@ -9778,7 +9838,7 @@
         <v>603</v>
       </c>
       <c r="W334" t="s">
-        <v>247</v>
+        <v>598</v>
       </c>
       <c r="X334" t="s">
         <v>257</v>
@@ -9792,7 +9852,7 @@
         <v>604</v>
       </c>
       <c r="W335" t="s">
-        <v>247</v>
+        <v>598</v>
       </c>
       <c r="X335" t="s">
         <v>257</v>
@@ -9806,7 +9866,7 @@
         <v>605</v>
       </c>
       <c r="W336" t="s">
-        <v>284</v>
+        <v>598</v>
       </c>
       <c r="X336" t="s">
         <v>257</v>
@@ -9820,7 +9880,7 @@
         <v>606</v>
       </c>
       <c r="W337" t="s">
-        <v>284</v>
+        <v>598</v>
       </c>
       <c r="X337" t="s">
         <v>257</v>
@@ -9834,7 +9894,7 @@
         <v>607</v>
       </c>
       <c r="W338" t="s">
-        <v>249</v>
+        <v>598</v>
       </c>
       <c r="X338" t="s">
         <v>257</v>
@@ -9848,7 +9908,7 @@
         <v>608</v>
       </c>
       <c r="W339" t="s">
-        <v>249</v>
+        <v>598</v>
       </c>
       <c r="X339" t="s">
         <v>257</v>
@@ -9862,7 +9922,7 @@
         <v>609</v>
       </c>
       <c r="W340" t="s">
-        <v>236</v>
+        <v>598</v>
       </c>
       <c r="X340" t="s">
         <v>257</v>
@@ -9876,7 +9936,7 @@
         <v>610</v>
       </c>
       <c r="W341" t="s">
-        <v>236</v>
+        <v>598</v>
       </c>
       <c r="X341" t="s">
         <v>257</v>
@@ -9890,7 +9950,7 @@
         <v>611</v>
       </c>
       <c r="W342" t="s">
-        <v>324</v>
+        <v>253</v>
       </c>
       <c r="X342" t="s">
         <v>257</v>
@@ -9904,7 +9964,7 @@
         <v>612</v>
       </c>
       <c r="W343" t="s">
-        <v>324</v>
+        <v>253</v>
       </c>
       <c r="X343" t="s">
         <v>257</v>
@@ -9918,7 +9978,7 @@
         <v>613</v>
       </c>
       <c r="W344" t="s">
-        <v>338</v>
+        <v>253</v>
       </c>
       <c r="X344" t="s">
         <v>257</v>
@@ -9932,7 +9992,7 @@
         <v>614</v>
       </c>
       <c r="W345" t="s">
-        <v>338</v>
+        <v>250</v>
       </c>
       <c r="X345" t="s">
         <v>257</v>
@@ -9946,7 +10006,7 @@
         <v>615</v>
       </c>
       <c r="W346" t="s">
-        <v>352</v>
+        <v>250</v>
       </c>
       <c r="X346" t="s">
         <v>257</v>
@@ -9960,7 +10020,7 @@
         <v>616</v>
       </c>
       <c r="W347" t="s">
-        <v>352</v>
+        <v>247</v>
       </c>
       <c r="X347" t="s">
         <v>257</v>
@@ -9974,7 +10034,7 @@
         <v>617</v>
       </c>
       <c r="W348" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="X348" t="s">
         <v>257</v>
@@ -9988,7 +10048,7 @@
         <v>618</v>
       </c>
       <c r="W349" t="s">
-        <v>251</v>
+        <v>284</v>
       </c>
       <c r="X349" t="s">
         <v>257</v>
@@ -10002,7 +10062,7 @@
         <v>619</v>
       </c>
       <c r="W350" t="s">
-        <v>379</v>
+        <v>284</v>
       </c>
       <c r="X350" t="s">
         <v>257</v>
@@ -10016,7 +10076,7 @@
         <v>620</v>
       </c>
       <c r="W351" t="s">
-        <v>379</v>
+        <v>249</v>
       </c>
       <c r="X351" t="s">
         <v>257</v>
@@ -10030,7 +10090,7 @@
         <v>621</v>
       </c>
       <c r="W352" t="s">
-        <v>393</v>
+        <v>249</v>
       </c>
       <c r="X352" t="s">
         <v>257</v>
@@ -10044,7 +10104,7 @@
         <v>622</v>
       </c>
       <c r="W353" t="s">
-        <v>393</v>
+        <v>236</v>
       </c>
       <c r="X353" t="s">
         <v>257</v>
@@ -10058,7 +10118,7 @@
         <v>623</v>
       </c>
       <c r="W354" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="X354" t="s">
         <v>257</v>
@@ -10072,7 +10132,7 @@
         <v>624</v>
       </c>
       <c r="W355" t="s">
-        <v>244</v>
+        <v>324</v>
       </c>
       <c r="X355" t="s">
         <v>257</v>
@@ -10086,7 +10146,7 @@
         <v>625</v>
       </c>
       <c r="W356" t="s">
-        <v>248</v>
+        <v>324</v>
       </c>
       <c r="X356" t="s">
         <v>257</v>
@@ -10100,7 +10160,7 @@
         <v>626</v>
       </c>
       <c r="W357" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="X357" t="s">
         <v>257</v>
@@ -10114,7 +10174,7 @@
         <v>627</v>
       </c>
       <c r="W358" t="s">
-        <v>433</v>
+        <v>246</v>
       </c>
       <c r="X358" t="s">
         <v>257</v>
@@ -10128,7 +10188,7 @@
         <v>628</v>
       </c>
       <c r="W359" t="s">
-        <v>433</v>
+        <v>351</v>
       </c>
       <c r="X359" t="s">
         <v>257</v>
@@ -10142,7 +10202,7 @@
         <v>629</v>
       </c>
       <c r="W360" t="s">
-        <v>447</v>
+        <v>351</v>
       </c>
       <c r="X360" t="s">
         <v>257</v>
@@ -10156,7 +10216,7 @@
         <v>630</v>
       </c>
       <c r="W361" t="s">
-        <v>447</v>
+        <v>365</v>
       </c>
       <c r="X361" t="s">
         <v>257</v>
@@ -10170,7 +10230,7 @@
         <v>631</v>
       </c>
       <c r="W362" t="s">
-        <v>461</v>
+        <v>365</v>
       </c>
       <c r="X362" t="s">
         <v>257</v>
@@ -10184,7 +10244,7 @@
         <v>632</v>
       </c>
       <c r="W363" t="s">
-        <v>461</v>
+        <v>251</v>
       </c>
       <c r="X363" t="s">
         <v>257</v>
@@ -10198,7 +10258,7 @@
         <v>633</v>
       </c>
       <c r="W364" t="s">
-        <v>475</v>
+        <v>251</v>
       </c>
       <c r="X364" t="s">
         <v>257</v>
@@ -10212,7 +10272,7 @@
         <v>634</v>
       </c>
       <c r="W365" t="s">
-        <v>475</v>
+        <v>392</v>
       </c>
       <c r="X365" t="s">
         <v>257</v>
@@ -10226,7 +10286,7 @@
         <v>635</v>
       </c>
       <c r="W366" t="s">
-        <v>489</v>
+        <v>392</v>
       </c>
       <c r="X366" t="s">
         <v>257</v>
@@ -10240,7 +10300,7 @@
         <v>636</v>
       </c>
       <c r="W367" t="s">
-        <v>489</v>
+        <v>406</v>
       </c>
       <c r="X367" t="s">
         <v>257</v>
@@ -10254,7 +10314,7 @@
         <v>637</v>
       </c>
       <c r="W368" t="s">
-        <v>242</v>
+        <v>406</v>
       </c>
       <c r="X368" t="s">
         <v>257</v>
@@ -10268,7 +10328,7 @@
         <v>638</v>
       </c>
       <c r="W369" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="X369" t="s">
         <v>257</v>
@@ -10282,7 +10342,7 @@
         <v>639</v>
       </c>
       <c r="W370" t="s">
-        <v>516</v>
+        <v>244</v>
       </c>
       <c r="X370" t="s">
         <v>257</v>
@@ -10296,7 +10356,7 @@
         <v>640</v>
       </c>
       <c r="W371" t="s">
-        <v>516</v>
+        <v>248</v>
       </c>
       <c r="X371" t="s">
         <v>257</v>
@@ -10310,7 +10370,7 @@
         <v>641</v>
       </c>
       <c r="W372" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="X372" t="s">
         <v>257</v>
@@ -10324,7 +10384,7 @@
         <v>642</v>
       </c>
       <c r="W373" t="s">
-        <v>254</v>
+        <v>446</v>
       </c>
       <c r="X373" t="s">
         <v>257</v>
@@ -10338,7 +10398,7 @@
         <v>643</v>
       </c>
       <c r="W374" t="s">
-        <v>543</v>
+        <v>446</v>
       </c>
       <c r="X374" t="s">
         <v>257</v>
@@ -10352,7 +10412,7 @@
         <v>644</v>
       </c>
       <c r="W375" t="s">
-        <v>543</v>
+        <v>460</v>
       </c>
       <c r="X375" t="s">
         <v>257</v>
@@ -10366,7 +10426,7 @@
         <v>645</v>
       </c>
       <c r="W376" t="s">
-        <v>557</v>
+        <v>460</v>
       </c>
       <c r="X376" t="s">
         <v>257</v>
@@ -10380,7 +10440,7 @@
         <v>646</v>
       </c>
       <c r="W377" t="s">
-        <v>557</v>
+        <v>474</v>
       </c>
       <c r="X377" t="s">
         <v>257</v>
@@ -10394,7 +10454,7 @@
         <v>647</v>
       </c>
       <c r="W378" t="s">
-        <v>571</v>
+        <v>474</v>
       </c>
       <c r="X378" t="s">
         <v>257</v>
@@ -10408,7 +10468,7 @@
         <v>648</v>
       </c>
       <c r="W379" t="s">
-        <v>571</v>
+        <v>488</v>
       </c>
       <c r="X379" t="s">
         <v>257</v>
@@ -10422,7 +10482,7 @@
         <v>649</v>
       </c>
       <c r="W380" t="s">
-        <v>585</v>
+        <v>488</v>
       </c>
       <c r="X380" t="s">
         <v>257</v>
@@ -10436,7 +10496,7 @@
         <v>650</v>
       </c>
       <c r="W381" t="s">
-        <v>585</v>
+        <v>502</v>
       </c>
       <c r="X381" t="s">
         <v>257</v>
@@ -10450,7 +10510,7 @@
         <v>651</v>
       </c>
       <c r="W382" t="s">
-        <v>253</v>
+        <v>502</v>
       </c>
       <c r="X382" t="s">
         <v>257</v>
@@ -10464,9 +10524,275 @@
         <v>652</v>
       </c>
       <c r="W383" t="s">
+        <v>242</v>
+      </c>
+      <c r="X383" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="384" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U384" t="s">
+        <v>91</v>
+      </c>
+      <c r="V384" t="s">
+        <v>653</v>
+      </c>
+      <c r="W384" t="s">
+        <v>242</v>
+      </c>
+      <c r="X384" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="385" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U385" t="s">
+        <v>91</v>
+      </c>
+      <c r="V385" t="s">
+        <v>654</v>
+      </c>
+      <c r="W385" t="s">
+        <v>529</v>
+      </c>
+      <c r="X385" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="386" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U386" t="s">
+        <v>91</v>
+      </c>
+      <c r="V386" t="s">
+        <v>655</v>
+      </c>
+      <c r="W386" t="s">
+        <v>529</v>
+      </c>
+      <c r="X386" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="387" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U387" t="s">
+        <v>91</v>
+      </c>
+      <c r="V387" t="s">
+        <v>656</v>
+      </c>
+      <c r="W387" t="s">
+        <v>254</v>
+      </c>
+      <c r="X387" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="388" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U388" t="s">
+        <v>91</v>
+      </c>
+      <c r="V388" t="s">
+        <v>657</v>
+      </c>
+      <c r="W388" t="s">
+        <v>254</v>
+      </c>
+      <c r="X388" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="389" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U389" t="s">
+        <v>91</v>
+      </c>
+      <c r="V389" t="s">
+        <v>658</v>
+      </c>
+      <c r="W389" t="s">
+        <v>556</v>
+      </c>
+      <c r="X389" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="390" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U390" t="s">
+        <v>91</v>
+      </c>
+      <c r="V390" t="s">
+        <v>659</v>
+      </c>
+      <c r="W390" t="s">
+        <v>556</v>
+      </c>
+      <c r="X390" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="391" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U391" t="s">
+        <v>91</v>
+      </c>
+      <c r="V391" t="s">
+        <v>660</v>
+      </c>
+      <c r="W391" t="s">
+        <v>570</v>
+      </c>
+      <c r="X391" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="392" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U392" t="s">
+        <v>91</v>
+      </c>
+      <c r="V392" t="s">
+        <v>661</v>
+      </c>
+      <c r="W392" t="s">
+        <v>570</v>
+      </c>
+      <c r="X392" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="393" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U393" t="s">
+        <v>91</v>
+      </c>
+      <c r="V393" t="s">
+        <v>662</v>
+      </c>
+      <c r="W393" t="s">
+        <v>584</v>
+      </c>
+      <c r="X393" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="394" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U394" t="s">
+        <v>91</v>
+      </c>
+      <c r="V394" t="s">
+        <v>663</v>
+      </c>
+      <c r="W394" t="s">
+        <v>584</v>
+      </c>
+      <c r="X394" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="395" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U395" t="s">
+        <v>91</v>
+      </c>
+      <c r="V395" t="s">
+        <v>664</v>
+      </c>
+      <c r="W395" t="s">
+        <v>598</v>
+      </c>
+      <c r="X395" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="396" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U396" t="s">
+        <v>91</v>
+      </c>
+      <c r="V396" t="s">
+        <v>665</v>
+      </c>
+      <c r="W396" t="s">
+        <v>598</v>
+      </c>
+      <c r="X396" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="397" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U397" t="s">
+        <v>91</v>
+      </c>
+      <c r="V397" t="s">
+        <v>666</v>
+      </c>
+      <c r="W397" t="s">
+        <v>252</v>
+      </c>
+      <c r="X397" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="398" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U398" t="s">
+        <v>91</v>
+      </c>
+      <c r="V398" t="s">
+        <v>667</v>
+      </c>
+      <c r="W398" t="s">
+        <v>252</v>
+      </c>
+      <c r="X398" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="399" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U399" t="s">
+        <v>91</v>
+      </c>
+      <c r="V399" t="s">
+        <v>668</v>
+      </c>
+      <c r="W399" t="s">
+        <v>669</v>
+      </c>
+      <c r="X399" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="400" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U400" t="s">
+        <v>91</v>
+      </c>
+      <c r="V400" t="s">
+        <v>670</v>
+      </c>
+      <c r="W400" t="s">
+        <v>669</v>
+      </c>
+      <c r="X400" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="401" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U401" t="s">
+        <v>91</v>
+      </c>
+      <c r="V401" t="s">
+        <v>671</v>
+      </c>
+      <c r="W401" t="s">
         <v>253</v>
       </c>
-      <c r="X383" t="s">
+      <c r="X401" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="402" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U402" t="s">
+        <v>91</v>
+      </c>
+      <c r="V402" t="s">
+        <v>672</v>
+      </c>
+      <c r="W402" t="s">
+        <v>253</v>
+      </c>
+      <c r="X402" t="s">
         <v>257</v>
       </c>
     </row>
